--- a/public/aditest.xlsx
+++ b/public/aditest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myweb\tmdi_20260520\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEB93E7-B80D-42DF-BABC-808A13645979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAF2CDE-B254-4F02-B25F-5289D73207C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{825ADABA-2C75-4D66-A0C5-FF85A49EC971}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="284">
   <si>
     <t>Year</t>
   </si>
@@ -46,10 +46,6 @@
   </si>
   <si>
     <t>codex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>test</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1281,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC4C66E6-80BB-4985-8426-CA57FFD46253}">
-  <dimension ref="A1:D271"/>
+  <dimension ref="A1:D270"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
@@ -1295,15 +1291,15 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>2011</v>
@@ -1317,7 +1313,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>2010</v>
@@ -1331,27 +1327,27 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>1994</v>
+        <v>2030</v>
       </c>
       <c r="C4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C5">
-        <v>0.3</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D5" t="s">
         <v>2</v>
@@ -1359,13 +1355,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C6">
-        <v>7.0000000000000007E-2</v>
+        <v>0.03</v>
       </c>
       <c r="D6" t="s">
         <v>2</v>
@@ -1376,10 +1372,10 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C7">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="D7" t="s">
         <v>2</v>
@@ -1390,10 +1386,10 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C8">
-        <v>0.08</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
         <v>2</v>
@@ -1404,10 +1400,10 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="D9" t="s">
         <v>2</v>
@@ -1418,10 +1414,10 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C10">
-        <v>0.9</v>
+        <v>0.03</v>
       </c>
       <c r="D10" t="s">
         <v>2</v>
@@ -1432,10 +1428,10 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C11">
-        <v>0.03</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D11" t="s">
         <v>2</v>
@@ -1446,10 +1442,10 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C12">
-        <v>3.0000000000000001E-3</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D12" t="s">
         <v>2</v>
@@ -1460,10 +1456,10 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C13">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="D13" t="s">
         <v>2</v>
@@ -1474,10 +1470,10 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C14">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="D14" t="s">
         <v>2</v>
@@ -1488,7 +1484,7 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C15">
         <v>0.01</v>
@@ -1502,10 +1498,10 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C16">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="D16" t="s">
         <v>2</v>
@@ -1516,10 +1512,10 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C17">
-        <v>0.04</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D17" t="s">
         <v>2</v>
@@ -1530,10 +1526,10 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C18">
-        <v>8.9999999999999993E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="D18" t="s">
         <v>2</v>
@@ -1544,10 +1540,10 @@
         <v>21</v>
       </c>
       <c r="B19">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C19">
-        <v>5.0000000000000001E-4</v>
+        <v>0.1</v>
       </c>
       <c r="D19" t="s">
         <v>2</v>
@@ -1558,10 +1554,10 @@
         <v>22</v>
       </c>
       <c r="B20">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C20">
-        <v>0.1</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D20" t="s">
         <v>2</v>
@@ -1572,10 +1568,10 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C21">
-        <v>8.0000000000000002E-3</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
         <v>2</v>
@@ -1586,10 +1582,10 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="D22" t="s">
         <v>2</v>
@@ -1600,10 +1596,10 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C23">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D23" t="s">
         <v>2</v>
@@ -1614,10 +1610,10 @@
         <v>26</v>
       </c>
       <c r="B24">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C24">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D24" t="s">
         <v>2</v>
@@ -1628,10 +1624,10 @@
         <v>27</v>
       </c>
       <c r="B25">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C25">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="D25" t="s">
         <v>2</v>
@@ -1642,10 +1638,10 @@
         <v>28</v>
       </c>
       <c r="B26">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C26">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="D26" t="s">
         <v>2</v>
@@ -1656,10 +1652,10 @@
         <v>29</v>
       </c>
       <c r="B27">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C27">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="D27" t="s">
         <v>2</v>
@@ -1670,10 +1666,10 @@
         <v>30</v>
       </c>
       <c r="B28">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C28">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="D28" t="s">
         <v>2</v>
@@ -1684,10 +1680,10 @@
         <v>31</v>
       </c>
       <c r="B29">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C29">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D29" t="s">
         <v>2</v>
@@ -1698,10 +1694,10 @@
         <v>32</v>
       </c>
       <c r="B30">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C30">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D30" t="s">
         <v>2</v>
@@ -1712,10 +1708,10 @@
         <v>33</v>
       </c>
       <c r="B31">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C31">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="D31" t="s">
         <v>2</v>
@@ -1726,10 +1722,10 @@
         <v>34</v>
       </c>
       <c r="B32">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C32">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D32" t="s">
         <v>2</v>
@@ -1740,7 +1736,7 @@
         <v>35</v>
       </c>
       <c r="B33">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C33">
         <v>0.02</v>
@@ -1754,7 +1750,7 @@
         <v>36</v>
       </c>
       <c r="B34">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C34">
         <v>0.02</v>
@@ -1768,10 +1764,10 @@
         <v>37</v>
       </c>
       <c r="B35">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C35">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D35" t="s">
         <v>2</v>
@@ -1782,10 +1778,10 @@
         <v>38</v>
       </c>
       <c r="B36">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C36">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="D36" t="s">
         <v>2</v>
@@ -1796,10 +1792,10 @@
         <v>39</v>
       </c>
       <c r="B37">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C37">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="D37" t="s">
         <v>2</v>
@@ -1810,10 +1806,10 @@
         <v>40</v>
       </c>
       <c r="B38">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C38">
-        <v>0.01</v>
+        <v>0.3</v>
       </c>
       <c r="D38" t="s">
         <v>2</v>
@@ -1824,10 +1820,10 @@
         <v>41</v>
       </c>
       <c r="B39">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C39">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="D39" t="s">
         <v>2</v>
@@ -1838,10 +1834,10 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C40">
-        <v>0.01</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D40" t="s">
         <v>2</v>
@@ -1852,10 +1848,10 @@
         <v>43</v>
       </c>
       <c r="B41">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C41">
-        <v>4.0000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="D41" t="s">
         <v>2</v>
@@ -1866,10 +1862,10 @@
         <v>44</v>
       </c>
       <c r="B42">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C42">
-        <v>2E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D42" t="s">
         <v>2</v>
@@ -1880,10 +1876,10 @@
         <v>45</v>
       </c>
       <c r="B43">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C43">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D43" t="s">
         <v>2</v>
@@ -1894,10 +1890,10 @@
         <v>46</v>
       </c>
       <c r="B44">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C44">
-        <v>0.02</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D44" t="s">
         <v>2</v>
@@ -1908,10 +1904,10 @@
         <v>47</v>
       </c>
       <c r="B45">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C45">
-        <v>7.0000000000000007E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D45" t="s">
         <v>2</v>
@@ -1922,10 +1918,10 @@
         <v>48</v>
       </c>
       <c r="B46">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C46">
-        <v>0.02</v>
+        <v>1E-3</v>
       </c>
       <c r="D46" t="s">
         <v>2</v>
@@ -1936,10 +1932,10 @@
         <v>49</v>
       </c>
       <c r="B47">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C47">
-        <v>1E-3</v>
+        <v>0.2</v>
       </c>
       <c r="D47" t="s">
         <v>2</v>
@@ -1950,7 +1946,7 @@
         <v>50</v>
       </c>
       <c r="B48">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C48">
         <v>0.2</v>
@@ -1964,10 +1960,10 @@
         <v>51</v>
       </c>
       <c r="B49">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C49">
-        <v>0.2</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="D49" t="s">
         <v>2</v>
@@ -1978,10 +1974,10 @@
         <v>52</v>
       </c>
       <c r="B50">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C50">
-        <v>2.9999999999999997E-4</v>
+        <v>0.03</v>
       </c>
       <c r="D50" t="s">
         <v>2</v>
@@ -1992,10 +1988,10 @@
         <v>53</v>
       </c>
       <c r="B51">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C51">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D51" t="s">
         <v>2</v>
@@ -2006,10 +2002,10 @@
         <v>54</v>
       </c>
       <c r="B52">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C52">
-        <v>0.02</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="D52" t="s">
         <v>2</v>
@@ -2020,10 +2016,10 @@
         <v>55</v>
       </c>
       <c r="B53">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C53">
-        <v>4.0000000000000002E-4</v>
+        <v>0.03</v>
       </c>
       <c r="D53" t="s">
         <v>2</v>
@@ -2034,10 +2030,10 @@
         <v>56</v>
       </c>
       <c r="B54">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C54">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D54" t="s">
         <v>2</v>
@@ -2048,10 +2044,10 @@
         <v>57</v>
       </c>
       <c r="B55">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C55">
-        <v>0.05</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D55" t="s">
         <v>2</v>
@@ -2062,10 +2058,10 @@
         <v>58</v>
       </c>
       <c r="B56">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C56">
-        <v>6.0000000000000001E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="D56" t="s">
         <v>2</v>
@@ -2076,10 +2072,10 @@
         <v>59</v>
       </c>
       <c r="B57">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C57">
-        <v>8.0000000000000004E-4</v>
+        <v>0.03</v>
       </c>
       <c r="D57" t="s">
         <v>2</v>
@@ -2090,10 +2086,10 @@
         <v>60</v>
       </c>
       <c r="B58">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C58">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="D58" t="s">
         <v>2</v>
@@ -2104,10 +2100,10 @@
         <v>61</v>
       </c>
       <c r="B59">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C59">
-        <v>0.2</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D59" t="s">
         <v>2</v>
@@ -2118,10 +2114,10 @@
         <v>62</v>
       </c>
       <c r="B60">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C60">
-        <v>6.0000000000000001E-3</v>
+        <v>0.03</v>
       </c>
       <c r="D60" t="s">
         <v>2</v>
@@ -2132,10 +2128,10 @@
         <v>63</v>
       </c>
       <c r="B61">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C61">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D61" t="s">
         <v>2</v>
@@ -2146,10 +2142,10 @@
         <v>64</v>
       </c>
       <c r="B62">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C62">
-        <v>0.02</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D62" t="s">
         <v>2</v>
@@ -2160,10 +2156,10 @@
         <v>65</v>
       </c>
       <c r="B63">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C63">
-        <v>4.0000000000000001E-3</v>
+        <v>0.3</v>
       </c>
       <c r="D63" t="s">
         <v>2</v>
@@ -2174,10 +2170,10 @@
         <v>66</v>
       </c>
       <c r="B64">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C64">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="D64" t="s">
         <v>2</v>
@@ -2188,10 +2184,10 @@
         <v>67</v>
       </c>
       <c r="B65">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C65">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="D65" t="s">
         <v>2</v>
@@ -2202,10 +2198,10 @@
         <v>68</v>
       </c>
       <c r="B66">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C66">
-        <v>0.1</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D66" t="s">
         <v>2</v>
@@ -2216,10 +2212,10 @@
         <v>69</v>
       </c>
       <c r="B67">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C67">
-        <v>4.0000000000000001E-3</v>
+        <v>0.02</v>
       </c>
       <c r="D67" t="s">
         <v>2</v>
@@ -2230,10 +2226,10 @@
         <v>70</v>
       </c>
       <c r="B68">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C68">
-        <v>0.02</v>
+        <v>0.4</v>
       </c>
       <c r="D68" t="s">
         <v>2</v>
@@ -2244,10 +2240,10 @@
         <v>71</v>
       </c>
       <c r="B69">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C69">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="D69" t="s">
         <v>2</v>
@@ -2258,10 +2254,10 @@
         <v>72</v>
       </c>
       <c r="B70">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C70">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D70" t="s">
         <v>2</v>
@@ -2272,10 +2268,10 @@
         <v>73</v>
       </c>
       <c r="B71">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C71">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="D71" t="s">
         <v>2</v>
@@ -2286,10 +2282,10 @@
         <v>74</v>
       </c>
       <c r="B72">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C72">
-        <v>0.01</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D72" t="s">
         <v>2</v>
@@ -2300,10 +2296,10 @@
         <v>75</v>
       </c>
       <c r="B73">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C73">
-        <v>7.0000000000000001E-3</v>
+        <v>0.02</v>
       </c>
       <c r="D73" t="s">
         <v>2</v>
@@ -2314,10 +2310,10 @@
         <v>76</v>
       </c>
       <c r="B74">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C74">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="D74" t="s">
         <v>2</v>
@@ -2328,10 +2324,10 @@
         <v>77</v>
       </c>
       <c r="B75">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C75">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="D75" t="s">
         <v>2</v>
@@ -2342,10 +2338,10 @@
         <v>78</v>
       </c>
       <c r="B76">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="D76" t="s">
         <v>2</v>
@@ -2356,10 +2352,10 @@
         <v>79</v>
       </c>
       <c r="B77">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C77">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="D77" t="s">
         <v>2</v>
@@ -2370,10 +2366,10 @@
         <v>80</v>
       </c>
       <c r="B78">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="D78" t="s">
         <v>2</v>
@@ -2384,10 +2380,10 @@
         <v>81</v>
       </c>
       <c r="B79">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C79">
-        <v>6.9999999999999999E-4</v>
+        <v>0.03</v>
       </c>
       <c r="D79" t="s">
         <v>2</v>
@@ -2398,10 +2394,10 @@
         <v>82</v>
       </c>
       <c r="B80">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C80">
-        <v>0.03</v>
+        <v>3</v>
       </c>
       <c r="D80" t="s">
         <v>2</v>
@@ -2412,10 +2408,10 @@
         <v>83</v>
       </c>
       <c r="B81">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="D81" t="s">
         <v>2</v>
@@ -2426,10 +2422,10 @@
         <v>84</v>
       </c>
       <c r="B82">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C82">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="D82" t="s">
         <v>2</v>
@@ -2440,10 +2436,10 @@
         <v>85</v>
       </c>
       <c r="B83">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C83">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="D83" t="s">
         <v>2</v>
@@ -2454,10 +2450,10 @@
         <v>86</v>
       </c>
       <c r="B84">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C84">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D84" t="s">
         <v>2</v>
@@ -2468,10 +2464,10 @@
         <v>87</v>
       </c>
       <c r="B85">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C85">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D85" t="s">
         <v>2</v>
@@ -2482,10 +2478,10 @@
         <v>88</v>
       </c>
       <c r="B86">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C86">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D86" t="s">
         <v>2</v>
@@ -2496,10 +2492,10 @@
         <v>89</v>
       </c>
       <c r="B87">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C87">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="D87" t="s">
         <v>2</v>
@@ -2510,10 +2506,10 @@
         <v>90</v>
       </c>
       <c r="B88">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C88">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D88" t="s">
         <v>2</v>
@@ -2524,10 +2520,10 @@
         <v>91</v>
       </c>
       <c r="B89">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C89">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D89" t="s">
         <v>2</v>
@@ -2538,10 +2534,10 @@
         <v>92</v>
       </c>
       <c r="B90">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C90">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D90" t="s">
         <v>2</v>
@@ -2552,10 +2548,10 @@
         <v>93</v>
       </c>
       <c r="B91">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C91">
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="D91" t="s">
         <v>2</v>
@@ -2566,10 +2562,10 @@
         <v>94</v>
       </c>
       <c r="B92">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C92">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D92" t="s">
         <v>2</v>
@@ -2580,10 +2576,10 @@
         <v>95</v>
       </c>
       <c r="B93">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C93">
-        <v>0.1</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D93" t="s">
         <v>2</v>
@@ -2594,10 +2590,10 @@
         <v>96</v>
       </c>
       <c r="B94">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C94">
-        <v>4.0000000000000001E-3</v>
+        <v>0.02</v>
       </c>
       <c r="D94" t="s">
         <v>2</v>
@@ -2608,10 +2604,10 @@
         <v>97</v>
       </c>
       <c r="B95">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C95">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="D95" t="s">
         <v>2</v>
@@ -2622,10 +2618,10 @@
         <v>98</v>
       </c>
       <c r="B96">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C96">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D96" t="s">
         <v>2</v>
@@ -2636,10 +2632,10 @@
         <v>99</v>
       </c>
       <c r="B97">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C97">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="D97" t="s">
         <v>2</v>
@@ -2650,10 +2646,10 @@
         <v>100</v>
       </c>
       <c r="B98">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C98">
-        <v>0.01</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D98" t="s">
         <v>2</v>
@@ -2664,10 +2660,10 @@
         <v>101</v>
       </c>
       <c r="B99">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C99">
-        <v>8.9999999999999993E-3</v>
+        <v>4</v>
       </c>
       <c r="D99" t="s">
         <v>2</v>
@@ -2678,10 +2674,10 @@
         <v>102</v>
       </c>
       <c r="B100">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C100">
-        <v>4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="D100" t="s">
         <v>2</v>
@@ -2692,10 +2688,10 @@
         <v>103</v>
       </c>
       <c r="B101">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C101">
-        <v>2.9999999999999997E-4</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D101" t="s">
         <v>2</v>
@@ -2706,10 +2702,10 @@
         <v>104</v>
       </c>
       <c r="B102">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C102">
-        <v>5.0000000000000001E-3</v>
+        <v>0.1</v>
       </c>
       <c r="D102" t="s">
         <v>2</v>
@@ -2720,7 +2716,7 @@
         <v>105</v>
       </c>
       <c r="B103">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C103">
         <v>0.1</v>
@@ -2734,10 +2730,10 @@
         <v>106</v>
       </c>
       <c r="B104">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C104">
-        <v>0.1</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="D104" t="s">
         <v>2</v>
@@ -2748,10 +2744,10 @@
         <v>107</v>
       </c>
       <c r="B105">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C105">
-        <v>6.9999999999999999E-4</v>
+        <v>0.09</v>
       </c>
       <c r="D105" t="s">
         <v>2</v>
@@ -2762,10 +2758,10 @@
         <v>108</v>
       </c>
       <c r="B106">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C106">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="D106" t="s">
         <v>2</v>
@@ -2776,10 +2772,10 @@
         <v>109</v>
       </c>
       <c r="B107">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C107">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D107" t="s">
         <v>2</v>
@@ -2790,10 +2786,10 @@
         <v>110</v>
       </c>
       <c r="B108">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C108">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D108" t="s">
         <v>2</v>
@@ -2804,7 +2800,7 @@
         <v>111</v>
       </c>
       <c r="B109">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C109">
         <v>0.03</v>
@@ -2818,10 +2814,10 @@
         <v>112</v>
       </c>
       <c r="B110">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C110">
-        <v>0.03</v>
+        <v>0.4</v>
       </c>
       <c r="D110" t="s">
         <v>2</v>
@@ -2832,10 +2828,10 @@
         <v>113</v>
       </c>
       <c r="B111">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C111">
-        <v>0.4</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D111" t="s">
         <v>2</v>
@@ -2846,10 +2842,10 @@
         <v>114</v>
       </c>
       <c r="B112">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C112">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="D112" t="s">
         <v>2</v>
@@ -2860,10 +2856,10 @@
         <v>115</v>
       </c>
       <c r="B113">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C113">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D113" t="s">
         <v>2</v>
@@ -2874,10 +2870,10 @@
         <v>116</v>
       </c>
       <c r="B114">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C114">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="D114" t="s">
         <v>2</v>
@@ -2888,7 +2884,7 @@
         <v>117</v>
       </c>
       <c r="B115">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C115">
         <v>0.2</v>
@@ -2902,10 +2898,10 @@
         <v>118</v>
       </c>
       <c r="B116">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C116">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D116" t="s">
         <v>2</v>
@@ -2916,10 +2912,10 @@
         <v>119</v>
       </c>
       <c r="B117">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C117">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D117" t="s">
         <v>2</v>
@@ -2930,10 +2926,10 @@
         <v>120</v>
       </c>
       <c r="B118">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C118">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D118" t="s">
         <v>2</v>
@@ -2944,10 +2940,10 @@
         <v>121</v>
       </c>
       <c r="B119">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C119">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D119" t="s">
         <v>2</v>
@@ -2958,10 +2954,10 @@
         <v>122</v>
       </c>
       <c r="B120">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C120">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D120" t="s">
         <v>2</v>
@@ -2972,10 +2968,10 @@
         <v>123</v>
       </c>
       <c r="B121">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C121">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D121" t="s">
         <v>2</v>
@@ -2986,10 +2982,10 @@
         <v>124</v>
       </c>
       <c r="B122">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C122">
-        <v>0.03</v>
+        <v>0.5</v>
       </c>
       <c r="D122" t="s">
         <v>2</v>
@@ -3000,10 +2996,10 @@
         <v>125</v>
       </c>
       <c r="B123">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C123">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="D123" t="s">
         <v>2</v>
@@ -3014,10 +3010,10 @@
         <v>126</v>
       </c>
       <c r="B124">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C124">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D124" t="s">
         <v>2</v>
@@ -3028,10 +3024,10 @@
         <v>127</v>
       </c>
       <c r="B125">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C125">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D125" t="s">
         <v>2</v>
@@ -3042,10 +3038,10 @@
         <v>128</v>
       </c>
       <c r="B126">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C126">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D126" t="s">
         <v>2</v>
@@ -3056,10 +3052,10 @@
         <v>129</v>
       </c>
       <c r="B127">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C127">
-        <v>0.02</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D127" t="s">
         <v>2</v>
@@ -3070,10 +3066,10 @@
         <v>130</v>
       </c>
       <c r="B128">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C128">
-        <v>5.0000000000000001E-3</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="D128" t="s">
         <v>2</v>
@@ -3084,10 +3080,10 @@
         <v>131</v>
       </c>
       <c r="B129">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C129">
-        <v>5.9999999999999995E-4</v>
+        <v>0.01</v>
       </c>
       <c r="D129" t="s">
         <v>2</v>
@@ -3098,10 +3094,10 @@
         <v>132</v>
       </c>
       <c r="B130">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C130">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="D130" t="s">
         <v>2</v>
@@ -3112,10 +3108,10 @@
         <v>133</v>
       </c>
       <c r="B131">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C131">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="D131" t="s">
         <v>2</v>
@@ -3126,10 +3122,10 @@
         <v>134</v>
       </c>
       <c r="B132">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C132">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="D132" t="s">
         <v>2</v>
@@ -3140,7 +3136,7 @@
         <v>135</v>
       </c>
       <c r="B133">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C133">
         <v>0.03</v>
@@ -3154,10 +3150,10 @@
         <v>136</v>
       </c>
       <c r="B134">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C134">
-        <v>0.03</v>
+        <v>1E-3</v>
       </c>
       <c r="D134" t="s">
         <v>2</v>
@@ -3168,10 +3164,10 @@
         <v>137</v>
       </c>
       <c r="B135">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C135">
-        <v>1E-3</v>
+        <v>0.05</v>
       </c>
       <c r="D135" t="s">
         <v>2</v>
@@ -3182,10 +3178,10 @@
         <v>138</v>
       </c>
       <c r="B136">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C136">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D136" t="s">
         <v>2</v>
@@ -3196,10 +3192,10 @@
         <v>139</v>
       </c>
       <c r="B137">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C137">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="D137" t="s">
         <v>2</v>
@@ -3210,10 +3206,10 @@
         <v>140</v>
       </c>
       <c r="B138">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C138">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="D138" t="s">
         <v>2</v>
@@ -3224,10 +3220,10 @@
         <v>141</v>
       </c>
       <c r="B139">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C139">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="D139" t="s">
         <v>2</v>
@@ -3238,10 +3234,10 @@
         <v>142</v>
       </c>
       <c r="B140">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C140">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D140" t="s">
         <v>2</v>
@@ -3252,13 +3248,13 @@
         <v>143</v>
       </c>
       <c r="B141">
-        <v>2030</v>
+        <v>2013</v>
       </c>
       <c r="C141">
-        <v>0.5</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="D141" t="s">
-        <v>2</v>
+        <v>273</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -3266,13 +3262,13 @@
         <v>144</v>
       </c>
       <c r="B142">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C142">
-        <v>2.5000000000000001E-2</v>
+        <v>0.15</v>
       </c>
       <c r="D142" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -3280,13 +3276,13 @@
         <v>145</v>
       </c>
       <c r="B143">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="C143">
-        <v>0.15</v>
+        <v>3.8E-3</v>
       </c>
       <c r="D143" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -3294,13 +3290,13 @@
         <v>146</v>
       </c>
       <c r="B144">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="C144">
-        <v>3.8E-3</v>
+        <v>0.15</v>
       </c>
       <c r="D144" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -3308,13 +3304,13 @@
         <v>147</v>
       </c>
       <c r="B145">
-        <v>2018</v>
+        <v>2003</v>
       </c>
       <c r="C145">
-        <v>0.15</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D145" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -3322,10 +3318,10 @@
         <v>148</v>
       </c>
       <c r="B146">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="C146">
-        <v>7.0000000000000001E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D146" t="s">
         <v>274</v>
@@ -3336,13 +3332,13 @@
         <v>149</v>
       </c>
       <c r="B147">
-        <v>2018</v>
+        <v>2006</v>
       </c>
       <c r="C147">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D147" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -3350,13 +3346,13 @@
         <v>150</v>
       </c>
       <c r="B148">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C148">
-        <v>0.02</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D148" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -3364,13 +3360,13 @@
         <v>151</v>
       </c>
       <c r="B149">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C149">
-        <v>4.0000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D149" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -3378,13 +3374,13 @@
         <v>152</v>
       </c>
       <c r="B150">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C150">
-        <v>6.0000000000000001E-3</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="D150" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -3392,10 +3388,10 @@
         <v>153</v>
       </c>
       <c r="B151">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C151">
-        <v>3.4000000000000002E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D151" t="s">
         <v>276</v>
@@ -3406,10 +3402,10 @@
         <v>154</v>
       </c>
       <c r="B152">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="C152">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="D152" t="s">
         <v>277</v>
@@ -3420,13 +3416,13 @@
         <v>155</v>
       </c>
       <c r="B153">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C153">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D153" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -3434,10 +3430,10 @@
         <v>156</v>
       </c>
       <c r="B154">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C154">
-        <v>0.02</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D154" t="s">
         <v>277</v>
@@ -3448,13 +3444,13 @@
         <v>157</v>
       </c>
       <c r="B155">
-        <v>2018</v>
+        <v>2001</v>
       </c>
       <c r="C155">
-        <v>3.0000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D155" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -3462,13 +3458,13 @@
         <v>158</v>
       </c>
       <c r="B156">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C156">
-        <v>4.0000000000000001E-3</v>
+        <v>0.1</v>
       </c>
       <c r="D156" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -3479,10 +3475,10 @@
         <v>2002</v>
       </c>
       <c r="C157">
-        <v>0.1</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -3490,13 +3486,13 @@
         <v>160</v>
       </c>
       <c r="B158">
-        <v>2002</v>
+        <v>2016</v>
       </c>
       <c r="C158">
-        <v>8.0000000000000002E-3</v>
+        <v>5.0000000000000002E-5</v>
       </c>
       <c r="D158" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -3504,13 +3500,13 @@
         <v>161</v>
       </c>
       <c r="B159">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C159">
-        <v>5.0000000000000002E-5</v>
+        <v>0.09</v>
       </c>
       <c r="D159" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -3518,13 +3514,13 @@
         <v>162</v>
       </c>
       <c r="B160">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="C160">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="D160" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -3532,13 +3528,13 @@
         <v>163</v>
       </c>
       <c r="B161">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="C161">
-        <v>0.05</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="D161" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -3549,10 +3545,10 @@
         <v>2020</v>
       </c>
       <c r="C162">
-        <v>2.9999999999999997E-4</v>
+        <v>0.15</v>
       </c>
       <c r="D162" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -3560,13 +3556,13 @@
         <v>165</v>
       </c>
       <c r="B163">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="C163">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="D163" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -3574,13 +3570,13 @@
         <v>166</v>
       </c>
       <c r="B164">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="C164">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D164" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -3588,13 +3584,13 @@
         <v>167</v>
       </c>
       <c r="B165">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="C165">
-        <v>0.05</v>
+        <v>2E-3</v>
       </c>
       <c r="D165" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -3602,13 +3598,13 @@
         <v>168</v>
       </c>
       <c r="B166">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C166">
-        <v>2E-3</v>
+        <v>0.2</v>
       </c>
       <c r="D166" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -3616,13 +3612,13 @@
         <v>169</v>
       </c>
       <c r="B167">
-        <v>2024</v>
+        <v>2008</v>
       </c>
       <c r="C167">
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="D167" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -3630,13 +3626,13 @@
         <v>170</v>
       </c>
       <c r="B168">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="C168">
-        <v>0.39</v>
+        <v>1.6E-2</v>
       </c>
       <c r="D168" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -3644,13 +3640,13 @@
         <v>171</v>
       </c>
       <c r="B169">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C169">
-        <v>1.6E-2</v>
+        <v>0.01</v>
       </c>
       <c r="D169" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -3658,13 +3654,13 @@
         <v>172</v>
       </c>
       <c r="B170">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="C170">
-        <v>0.01</v>
+        <v>1.6E-2</v>
       </c>
       <c r="D170" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -3672,13 +3668,13 @@
         <v>173</v>
       </c>
       <c r="B171">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="C171">
-        <v>1.6E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="D171" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -3686,13 +3682,13 @@
         <v>174</v>
       </c>
       <c r="B172">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="C172">
-        <v>1E-3</v>
+        <v>0.05</v>
       </c>
       <c r="D172" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -3700,13 +3696,13 @@
         <v>175</v>
       </c>
       <c r="B173">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C173">
-        <v>0.05</v>
+        <v>0.42</v>
       </c>
       <c r="D173" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -3714,13 +3710,13 @@
         <v>176</v>
       </c>
       <c r="B174">
-        <v>2022</v>
+        <v>2002</v>
       </c>
       <c r="C174">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="D174" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -3728,13 +3724,13 @@
         <v>177</v>
       </c>
       <c r="B175">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="C175">
-        <v>0.26</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="D175" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -3742,13 +3738,13 @@
         <v>178</v>
       </c>
       <c r="B176">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="C176">
-        <v>6.0000000000000001E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="D176" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -3756,13 +3752,13 @@
         <v>179</v>
       </c>
       <c r="B177">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C177">
-        <v>7.0000000000000001E-3</v>
+        <v>0.05</v>
       </c>
       <c r="D177" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -3770,13 +3766,13 @@
         <v>180</v>
       </c>
       <c r="B178">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C178">
-        <v>0.05</v>
+        <v>3.9E-2</v>
       </c>
       <c r="D178" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -3784,13 +3780,13 @@
         <v>181</v>
       </c>
       <c r="B179">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="C179">
-        <v>3.9E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D179" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -3798,13 +3794,13 @@
         <v>182</v>
       </c>
       <c r="B180">
-        <v>2001</v>
+        <v>2021</v>
       </c>
       <c r="C180">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D180" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -3812,13 +3808,13 @@
         <v>183</v>
       </c>
       <c r="B181">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C181">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="D181" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -3826,13 +3822,13 @@
         <v>184</v>
       </c>
       <c r="B182">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C182">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D182" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -3840,13 +3836,13 @@
         <v>185</v>
       </c>
       <c r="B183">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="C183">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D183" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -3854,13 +3850,13 @@
         <v>186</v>
       </c>
       <c r="B184">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C184">
-        <v>0.02</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="D184" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -3868,13 +3864,13 @@
         <v>187</v>
       </c>
       <c r="B185">
-        <v>2022</v>
+        <v>8</v>
       </c>
       <c r="C185">
-        <v>4.9000000000000002E-2</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="D185" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -3882,13 +3878,13 @@
         <v>188</v>
       </c>
       <c r="B186">
-        <v>8</v>
+        <v>2015</v>
       </c>
       <c r="C186">
-        <v>7.3999999999999996E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="D186" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -3896,13 +3892,13 @@
         <v>189</v>
       </c>
       <c r="B187">
-        <v>2015</v>
+        <v>2008</v>
       </c>
       <c r="C187">
-        <v>1.6999999999999999E-3</v>
+        <v>0.39</v>
       </c>
       <c r="D187" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -3910,10 +3906,10 @@
         <v>190</v>
       </c>
       <c r="B188">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C188">
-        <v>0.39</v>
+        <v>0.04</v>
       </c>
       <c r="D188" t="s">
         <v>276</v>
@@ -3923,22 +3919,22 @@
       <c r="A189" t="s">
         <v>191</v>
       </c>
-      <c r="B189">
-        <v>2022</v>
-      </c>
       <c r="C189">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>192</v>
       </c>
+      <c r="B190">
+        <v>2004</v>
+      </c>
       <c r="C190">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D190" t="s">
         <v>274</v>
@@ -3949,13 +3945,13 @@
         <v>193</v>
       </c>
       <c r="B191">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="C191">
-        <v>0.3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="D191" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -3963,13 +3959,13 @@
         <v>194</v>
       </c>
       <c r="B192">
-        <v>2011</v>
+        <v>1986</v>
       </c>
       <c r="C192">
-        <v>5.0000000000000001E-4</v>
+        <v>0.12</v>
       </c>
       <c r="D192" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -3977,13 +3973,13 @@
         <v>195</v>
       </c>
       <c r="B193">
-        <v>1986</v>
+        <v>2021</v>
       </c>
       <c r="C193">
-        <v>0.12</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D193" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -3991,13 +3987,13 @@
         <v>196</v>
       </c>
       <c r="B194">
-        <v>2021</v>
+        <v>2007</v>
       </c>
       <c r="C194">
-        <v>1.4999999999999999E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="D194" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -4005,38 +4001,38 @@
         <v>197</v>
       </c>
       <c r="B195">
-        <v>2007</v>
+        <v>8</v>
       </c>
       <c r="C195">
-        <v>7.5999999999999998E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="D195" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>198</v>
       </c>
-      <c r="B196">
-        <v>8</v>
-      </c>
       <c r="C196">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D196" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>199</v>
       </c>
+      <c r="B197">
+        <v>2017</v>
+      </c>
       <c r="C197">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="D197" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -4044,13 +4040,13 @@
         <v>200</v>
       </c>
       <c r="B198">
-        <v>2017</v>
+        <v>2002</v>
       </c>
       <c r="C198">
-        <v>0.05</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="D198" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -4058,13 +4054,13 @@
         <v>201</v>
       </c>
       <c r="B199">
-        <v>2002</v>
+        <v>2016</v>
       </c>
       <c r="C199">
-        <v>8.9999999999999998E-4</v>
+        <v>0.03</v>
       </c>
       <c r="D199" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -4072,10 +4068,10 @@
         <v>202</v>
       </c>
       <c r="B200">
-        <v>2016</v>
+        <v>1993</v>
       </c>
       <c r="C200">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="D200" t="s">
         <v>274</v>
@@ -4085,28 +4081,28 @@
       <c r="A201" t="s">
         <v>203</v>
       </c>
-      <c r="B201">
-        <v>1993</v>
+      <c r="B201" t="s">
+        <v>278</v>
       </c>
       <c r="C201">
-        <v>0.01</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="D201" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>204</v>
       </c>
-      <c r="B202" t="s">
-        <v>279</v>
+      <c r="B202">
+        <v>1965</v>
       </c>
       <c r="C202">
-        <v>1.7000000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="D202" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -4114,13 +4110,13 @@
         <v>205</v>
       </c>
       <c r="B203">
-        <v>1965</v>
+        <v>2004</v>
       </c>
       <c r="C203">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="D203" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -4128,13 +4124,13 @@
         <v>206</v>
       </c>
       <c r="B204">
-        <v>2004</v>
+        <v>2016</v>
       </c>
       <c r="C204">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="D204" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -4142,13 +4138,13 @@
         <v>207</v>
       </c>
       <c r="B205">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="C205">
-        <v>0.6</v>
+        <v>0.02</v>
       </c>
       <c r="D205" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -4156,13 +4152,13 @@
         <v>208</v>
       </c>
       <c r="B206">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C206">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D206" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -4170,13 +4166,13 @@
         <v>209</v>
       </c>
       <c r="B207">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C207">
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D207" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -4187,10 +4183,10 @@
         <v>2014</v>
       </c>
       <c r="C208">
-        <v>1.4999999999999999E-2</v>
+        <v>0.05</v>
       </c>
       <c r="D208" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -4198,27 +4194,27 @@
         <v>211</v>
       </c>
       <c r="B209">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="C209">
-        <v>0.05</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="D209" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>212</v>
       </c>
-      <c r="B210">
-        <v>2007</v>
+      <c r="B210" t="s">
+        <v>279</v>
       </c>
       <c r="C210">
-        <v>3.3000000000000002E-2</v>
+        <v>1.5E-3</v>
       </c>
       <c r="D210" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -4229,24 +4225,24 @@
         <v>280</v>
       </c>
       <c r="C211">
-        <v>1.5E-3</v>
+        <v>0.03</v>
       </c>
       <c r="D211" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>214</v>
       </c>
-      <c r="B212" t="s">
-        <v>281</v>
+      <c r="B212">
+        <v>2017</v>
       </c>
       <c r="C212">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="D212" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -4254,41 +4250,41 @@
         <v>215</v>
       </c>
       <c r="B213">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="C213">
-        <v>0.3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D213" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>216</v>
       </c>
-      <c r="B214">
-        <v>2009</v>
+      <c r="B214" t="s">
+        <v>281</v>
       </c>
       <c r="C214">
-        <v>5.0000000000000001E-3</v>
+        <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>217</v>
       </c>
-      <c r="B215" t="s">
-        <v>282</v>
+      <c r="B215">
+        <v>2008</v>
       </c>
       <c r="C215">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="D215" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -4296,13 +4292,13 @@
         <v>218</v>
       </c>
       <c r="B216">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C216">
         <v>0.03</v>
       </c>
       <c r="D216" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -4310,27 +4306,27 @@
         <v>219</v>
       </c>
       <c r="B217">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="C217">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="D217" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>220</v>
       </c>
-      <c r="B218">
-        <v>2015</v>
+      <c r="B218" t="s">
+        <v>282</v>
       </c>
       <c r="C218">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="D218" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -4341,24 +4337,24 @@
         <v>283</v>
       </c>
       <c r="C219">
-        <v>1.25</v>
+        <v>0.03</v>
       </c>
       <c r="D219" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>222</v>
       </c>
-      <c r="B220" t="s">
-        <v>284</v>
+      <c r="B220">
+        <v>2017</v>
       </c>
       <c r="C220">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D220" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -4366,13 +4362,13 @@
         <v>223</v>
       </c>
       <c r="B221">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="C221">
         <v>0.05</v>
       </c>
       <c r="D221" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -4380,13 +4376,13 @@
         <v>224</v>
       </c>
       <c r="B222">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C222">
-        <v>0.05</v>
+        <v>1.32</v>
       </c>
       <c r="D222" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -4394,13 +4390,13 @@
         <v>225</v>
       </c>
       <c r="B223">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C223">
-        <v>1.32</v>
+        <v>0.01</v>
       </c>
       <c r="D223" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -4408,13 +4404,13 @@
         <v>226</v>
       </c>
       <c r="B224">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="C224">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D224" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -4422,10 +4418,10 @@
         <v>227</v>
       </c>
       <c r="B225">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C225">
-        <v>0.03</v>
+        <v>2.3E-2</v>
       </c>
       <c r="D225" t="s">
         <v>275</v>
@@ -4436,13 +4432,13 @@
         <v>228</v>
       </c>
       <c r="B226">
-        <v>2022</v>
+        <v>1987</v>
       </c>
       <c r="C226">
-        <v>2.3E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D226" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -4450,10 +4446,10 @@
         <v>229</v>
       </c>
       <c r="B227">
-        <v>1987</v>
+        <v>2009</v>
       </c>
       <c r="C227">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="D227" t="s">
         <v>275</v>
@@ -4464,13 +4460,13 @@
         <v>230</v>
       </c>
       <c r="B228">
-        <v>2009</v>
+        <v>1988</v>
       </c>
       <c r="C228">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D228" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -4478,13 +4474,13 @@
         <v>231</v>
       </c>
       <c r="B229">
-        <v>1988</v>
+        <v>1998</v>
       </c>
       <c r="C229">
-        <v>0.02</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="D229" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -4492,13 +4488,13 @@
         <v>232</v>
       </c>
       <c r="B230">
-        <v>1998</v>
+        <v>2015</v>
       </c>
       <c r="C230">
-        <v>1.7000000000000001E-2</v>
+        <v>0.748</v>
       </c>
       <c r="D230" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -4506,13 +4502,13 @@
         <v>233</v>
       </c>
       <c r="B231">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C231">
-        <v>0.748</v>
+        <v>0.04</v>
       </c>
       <c r="D231" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -4520,13 +4516,13 @@
         <v>234</v>
       </c>
       <c r="B232">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C232">
-        <v>0.04</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="D232" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -4534,13 +4530,13 @@
         <v>235</v>
       </c>
       <c r="B233">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C233">
-        <v>1.2999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D233" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -4548,13 +4544,13 @@
         <v>236</v>
       </c>
       <c r="B234">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C234">
-        <v>0.02</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="D234" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -4562,10 +4558,10 @@
         <v>237</v>
       </c>
       <c r="B235">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C235">
-        <v>4.4000000000000003E-3</v>
+        <v>0.01</v>
       </c>
       <c r="D235" t="s">
         <v>276</v>
@@ -4576,13 +4572,13 @@
         <v>238</v>
       </c>
       <c r="B236">
-        <v>2021</v>
+        <v>2005</v>
       </c>
       <c r="C236">
-        <v>0.01</v>
+        <v>0.18</v>
       </c>
       <c r="D236" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -4590,13 +4586,13 @@
         <v>239</v>
       </c>
       <c r="B237">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="C237">
-        <v>0.18</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="D237" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -4604,13 +4600,13 @@
         <v>240</v>
       </c>
       <c r="B238">
-        <v>2022</v>
+        <v>1995</v>
       </c>
       <c r="C238">
-        <v>2.8000000000000001E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D238" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -4618,13 +4614,13 @@
         <v>241</v>
       </c>
       <c r="B239">
-        <v>1995</v>
+        <v>2025</v>
       </c>
       <c r="C239">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="D239" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -4632,13 +4628,13 @@
         <v>242</v>
       </c>
       <c r="B240">
-        <v>2025</v>
+        <v>2013</v>
       </c>
       <c r="C240">
-        <v>0.02</v>
+        <v>0.9</v>
       </c>
       <c r="D240" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -4646,13 +4642,13 @@
         <v>243</v>
       </c>
       <c r="B241">
-        <v>2013</v>
+        <v>1997</v>
       </c>
       <c r="C241">
-        <v>0.9</v>
+        <v>0.02</v>
       </c>
       <c r="D241" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -4660,13 +4656,13 @@
         <v>244</v>
       </c>
       <c r="B242">
-        <v>1997</v>
+        <v>2004</v>
       </c>
       <c r="C242">
-        <v>0.02</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D242" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -4674,13 +4670,13 @@
         <v>245</v>
       </c>
       <c r="B243">
-        <v>2004</v>
+        <v>2017</v>
       </c>
       <c r="C243">
-        <v>5.0000000000000001E-3</v>
+        <v>0.05</v>
       </c>
       <c r="D243" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -4688,10 +4684,10 @@
         <v>246</v>
       </c>
       <c r="B244">
-        <v>2017</v>
+        <v>1991</v>
       </c>
       <c r="C244">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D244" t="s">
         <v>274</v>
@@ -4702,13 +4698,13 @@
         <v>247</v>
       </c>
       <c r="B245">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="C245">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="D245" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -4716,13 +4712,13 @@
         <v>248</v>
       </c>
       <c r="B246">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C246">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D246" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -4730,13 +4726,13 @@
         <v>249</v>
       </c>
       <c r="B247">
-        <v>1998</v>
+        <v>2005</v>
       </c>
       <c r="C247">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="D247" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -4744,13 +4740,13 @@
         <v>250</v>
       </c>
       <c r="B248">
-        <v>2005</v>
+        <v>1985</v>
       </c>
       <c r="C248">
-        <v>0.01</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D248" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -4758,13 +4754,13 @@
         <v>251</v>
       </c>
       <c r="B249">
-        <v>1985</v>
+        <v>2010</v>
       </c>
       <c r="C249">
-        <v>7.0000000000000007E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D249" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -4772,13 +4768,13 @@
         <v>252</v>
       </c>
       <c r="B250">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C250">
-        <v>5.0000000000000001E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="D250" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -4786,13 +4782,13 @@
         <v>253</v>
       </c>
       <c r="B251">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C251">
-        <v>4.0000000000000002E-4</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="D251" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -4800,10 +4796,10 @@
         <v>254</v>
       </c>
       <c r="B252">
-        <v>2008</v>
+        <v>1991</v>
       </c>
       <c r="C252">
-        <v>1.2999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D252" t="s">
         <v>274</v>
@@ -4814,13 +4810,13 @@
         <v>255</v>
       </c>
       <c r="B253">
-        <v>1991</v>
+        <v>2013</v>
       </c>
       <c r="C253">
-        <v>0.02</v>
+        <v>0.23</v>
       </c>
       <c r="D253" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -4828,13 +4824,13 @@
         <v>256</v>
       </c>
       <c r="B254">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="C254">
-        <v>0.23</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="D254" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -4842,10 +4838,10 @@
         <v>257</v>
       </c>
       <c r="B255">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="C255">
-        <v>9.5999999999999992E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D255" t="s">
         <v>276</v>
@@ -4856,13 +4852,13 @@
         <v>258</v>
       </c>
       <c r="B256">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="C256">
-        <v>4.0000000000000001E-3</v>
+        <v>0.05</v>
       </c>
       <c r="D256" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -4870,13 +4866,13 @@
         <v>259</v>
       </c>
       <c r="B257">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C257">
-        <v>0.05</v>
+        <v>7.6E-3</v>
       </c>
       <c r="D257" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -4884,10 +4880,10 @@
         <v>260</v>
       </c>
       <c r="B258">
-        <v>2019</v>
+        <v>2002</v>
       </c>
       <c r="C258">
-        <v>7.6E-3</v>
+        <v>0.08</v>
       </c>
       <c r="D258" t="s">
         <v>276</v>
@@ -4898,10 +4894,10 @@
         <v>261</v>
       </c>
       <c r="B259">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="C259">
-        <v>0.08</v>
+        <v>1E-3</v>
       </c>
       <c r="D259" t="s">
         <v>277</v>
@@ -4912,13 +4908,13 @@
         <v>262</v>
       </c>
       <c r="B260">
-        <v>2014</v>
+        <v>1988</v>
       </c>
       <c r="C260">
-        <v>1E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D260" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -4926,13 +4922,13 @@
         <v>263</v>
       </c>
       <c r="B261">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="C261">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D261" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -4940,13 +4936,13 @@
         <v>264</v>
       </c>
       <c r="B262">
-        <v>1991</v>
+        <v>2021</v>
       </c>
       <c r="C262">
-        <v>5.0000000000000001E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D262" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -4954,13 +4950,13 @@
         <v>265</v>
       </c>
       <c r="B263">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C263">
-        <v>8.0000000000000002E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="D263" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -4968,10 +4964,10 @@
         <v>266</v>
       </c>
       <c r="B264">
-        <v>2015</v>
+        <v>2002</v>
       </c>
       <c r="C264">
-        <v>2E-3</v>
+        <v>0.2</v>
       </c>
       <c r="D264" t="s">
         <v>274</v>
@@ -4982,13 +4978,13 @@
         <v>267</v>
       </c>
       <c r="B265">
-        <v>2002</v>
+        <v>2020</v>
       </c>
       <c r="C265">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D265" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -4996,10 +4992,10 @@
         <v>268</v>
       </c>
       <c r="B266">
-        <v>2020</v>
+        <v>2009</v>
       </c>
       <c r="C266">
-        <v>0.1</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D266" t="s">
         <v>275</v>
@@ -5010,13 +5006,13 @@
         <v>269</v>
       </c>
       <c r="B267">
-        <v>2009</v>
+        <v>2020</v>
       </c>
       <c r="C267">
-        <v>2.4E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="D267" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -5024,10 +5020,10 @@
         <v>270</v>
       </c>
       <c r="B268">
-        <v>2020</v>
+        <v>1997</v>
       </c>
       <c r="C268">
-        <v>1E-3</v>
+        <v>0.02</v>
       </c>
       <c r="D268" t="s">
         <v>274</v>
@@ -5038,13 +5034,13 @@
         <v>271</v>
       </c>
       <c r="B269">
-        <v>1997</v>
+        <v>2019</v>
       </c>
       <c r="C269">
         <v>0.02</v>
       </c>
       <c r="D269" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -5055,24 +5051,10 @@
         <v>2019</v>
       </c>
       <c r="C270">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="D270" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A271" t="s">
-        <v>273</v>
-      </c>
-      <c r="B271">
-        <v>2019</v>
-      </c>
-      <c r="C271">
-        <v>0.2</v>
-      </c>
-      <c r="D271" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
